--- a/pipelines/Demo_data/In_data/group_export_lines.xlsx
+++ b/pipelines/Demo_data/In_data/group_export_lines.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Отдел</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>Итого</t>
+  </si>
+  <si>
+    <t>Лот</t>
   </si>
   <si>
     <t>Север</t>
@@ -84,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
@@ -92,6 +95,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
@@ -631,13 +635,16 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
@@ -646,16 +653,19 @@
         <v>50.549999999999997</v>
       </c>
       <c r="E2" s="1">
-        <f>C2*D2</f>
+        <f t="shared" ref="E2:E6" si="0">C2*D2</f>
         <v>151.64999999999998</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -663,17 +673,20 @@
       <c r="D3" s="2">
         <v>70.25</v>
       </c>
-      <c r="E3" s="3">
-        <f>C3*D3</f>
+      <c r="E3" s="4">
+        <f t="shared" si="0"/>
         <v>140.5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -681,17 +694,20 @@
       <c r="D4" s="2">
         <v>40</v>
       </c>
-      <c r="E4" s="3">
-        <f>C4*D4</f>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
         <v>200</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -699,17 +715,20 @@
       <c r="D5" s="2">
         <v>60</v>
       </c>
-      <c r="E5" s="3">
-        <f>C5*D5</f>
+      <c r="E5" s="4">
+        <f t="shared" si="0"/>
         <v>60</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -717,9 +736,12 @@
       <c r="D6" s="2">
         <v>35</v>
       </c>
-      <c r="E6" s="3">
-        <f>C6*D6</f>
+      <c r="E6" s="4">
+        <f t="shared" si="0"/>
         <v>140</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/pipelines/Demo_data/In_data/group_export_lines.xlsx
+++ b/pipelines/Demo_data/In_data/group_export_lines.xlsx
@@ -617,6 +617,7 @@
     <col customWidth="1" min="3" max="3" width="13.28125"/>
     <col customWidth="1" min="4" max="4" width="10.57421875"/>
     <col customWidth="1" min="5" max="5" width="13.57421875"/>
+    <col customWidth="1" min="6" max="6" width="24.00390625"/>
   </cols>
   <sheetData>
     <row r="1">
